--- a/event_feedback_forms/020_trunk_or_treat_judging_form--event_feedback_forms.xlsx
+++ b/event_feedback_forms/020_trunk_or_treat_judging_form--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form</t>
+          <t>trunk_or_treat_judging_form_event</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trunk</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,47 +538,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score</t>
+          <t>trunk_or_treat_judging_form_theme</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Theme</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score_comment</t>
+          <t>trunk_or_treat_judging_form_decorations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Please provide a brief comment for your score.</t>
-        </is>
-      </c>
+          <t>Decorations</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -588,40 +584,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_attended</t>
+          <t>trunk_or_treat_judging_form_food</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Attended</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_name</t>
+          <t>trunk_or_treat_judging_form_trunk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Trunk</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,40 +630,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_location</t>
+          <t>trunk_or_treat_judging_form_team_spirit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Team Spirit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_date</t>
+          <t>trunk_or_treat_judging_form_score</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time</t>
+          <t>trunk_or_treat_judging_form_attended</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Attended</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end</t>
+          <t>trunk_or_treat_judging_form_event_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -726,366 +722,48 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end_am_pm</t>
+          <t>trunk_or_treat_judging_form_location</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end_period</t>
+          <t>trunk_or_treat_judging_form_comment</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide a brief comment for the event</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_event_time_start</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_event_date</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_event_location</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_event</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Trunk</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_9</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>trunk_or_treat_judging_form_score_10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1105,9 +783,9 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,323 +808,323 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_theme_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>best_theme:_halloween</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Best Theme: Halloween</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_theme_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>best_use_of_lights:_decorative</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Best Use of Lights: Decorative</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_theme_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>best_overall:_outstanding</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Best Overall: Outstanding</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_decorations_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>best_food:_delicious</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Best Food: Delicious</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_decorations_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>best_trunk:_awesome</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Best Trunk: Awesome</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_food_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>best_use_of_theme:_creative</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Best Use of Theme: Creative</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_food_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>best_team_spirit:_excellent</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Best Team Spirit: Excellent</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_choices</t>
+          <t>trunk_or_treat_judging_form_food_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>best_costumes:_fun</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Best Costumes: Fun</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score_choices</t>
+          <t>trunk_or_treat_judging_form_trunk_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score_choices</t>
+          <t>trunk_or_treat_judging_form_trunk_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score_choices</t>
+          <t>trunk_or_treat_judging_form_trunk_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score_choices</t>
+          <t>trunk_or_treat_judging_form_team_spirit_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_score_choices</t>
+          <t>trunk_or_treat_judging_form_team_spirit_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_attended_choices</t>
+          <t>trunk_or_treat_judging_form_team_spirit_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_attended_choices</t>
+          <t>trunk_or_treat_judging_form_score_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end_am_pm_choices</t>
+          <t>trunk_or_treat_judging_form_score_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end_am_pm_choices</t>
+          <t>trunk_or_treat_judging_form_score_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>pm</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end_period_choices</t>
+          <t>trunk_or_treat_judging_form_attended_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trunk_or_treat_judging_form_event_time_end_period_choices</t>
+          <t>trunk_or_treat_judging_form_attended_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pm</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>False</t>
         </is>
       </c>
     </row>
